--- a/Course content/Chronogram.xlsx
+++ b/Course content/Chronogram.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\UAM\22-23\Master\Intro ML\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\UAM\22-23\Master\Intro ML\IMLEF\Course content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B948A51-F45C-43ED-8456-DCDD55CC9EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B3D9BE-6A19-42A1-AA42-7765D793FB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14160" xr2:uid="{C2A537E0-5460-478C-95AA-76C134CB1600}"/>
+    <workbookView xWindow="1100" yWindow="1100" windowWidth="19200" windowHeight="10160" xr2:uid="{C2A537E0-5460-478C-95AA-76C134CB1600}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>Basic concepts</t>
   </si>
@@ -195,33 +195,12 @@
     <t>HW#3 Lab session</t>
   </si>
   <si>
-    <t xml:space="preserve">Mon - Wed, Nov 7 - 9 </t>
-  </si>
-  <si>
-    <t>Tue - Wed, Nov 1-2</t>
-  </si>
-  <si>
     <t>Mon - Tue, Nov 14 - 15</t>
   </si>
   <si>
-    <t>Wed - Mon, Nov 16 - 21</t>
-  </si>
-  <si>
-    <t>Tue- Wed, Nov 22-23</t>
-  </si>
-  <si>
-    <t>Mon, Nov 29</t>
-  </si>
-  <si>
     <t>Wed, Nov 30</t>
   </si>
   <si>
-    <t>DIA 1 es FIESTA</t>
-  </si>
-  <si>
-    <t>DIA 9 es FIESTA</t>
-  </si>
-  <si>
     <t>HOML Ch. 3 / ISL Ch. 4</t>
   </si>
   <si>
@@ -243,23 +222,38 @@
     <t>Thu, Oct 20</t>
   </si>
   <si>
-    <t>HW#1 Lab Session Voluntary</t>
-  </si>
-  <si>
-    <t>Fri, Oct 21</t>
-  </si>
-  <si>
     <t>1 weeks</t>
   </si>
   <si>
     <t>Mon - Tue, Oct 24 - 25</t>
+  </si>
+  <si>
+    <t>Wed - Mon, Oct 26-31</t>
+  </si>
+  <si>
+    <t>Wed, Nov 2</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Mon - Tue, Nov 7 - 8</t>
+  </si>
+  <si>
+    <t>Wed, Nov 29</t>
+  </si>
+  <si>
+    <t>Tue, Nov 16</t>
+  </si>
+  <si>
+    <t>Emmanuelle Mendes Pino (UAH)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,8 +284,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -316,14 +317,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -331,35 +326,274 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -674,205 +908,197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCDD6C8F-8A48-4023-B5FE-AD1097B60F0C}">
-  <dimension ref="B3:E21"/>
+  <dimension ref="B2:E20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="53.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="11" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2" t="s">
-        <v>41</v>
+      <c r="C4" s="22"/>
+      <c r="D4" s="12" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>36</v>
+      <c r="C5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>37</v>
+      <c r="C6" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>38</v>
+      <c r="C7" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B8" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9" t="s">
-        <v>40</v>
+      <c r="B8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="D8" s="14" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2" t="s">
-        <v>19</v>
+      <c r="B9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C10" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B12" s="6" t="s">
+      <c r="D10" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="24"/>
+      <c r="D11" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="26"/>
+    </row>
+    <row r="12" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
-        <v>31</v>
+      <c r="D12" s="17" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="10" t="s">
-        <v>25</v>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="18" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="11" t="s">
-        <v>18</v>
-      </c>
+      <c r="B14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>26</v>
+      <c r="D15" s="15" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="C16" s="23"/>
+      <c r="D16" s="15" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="10" t="s">
-        <v>28</v>
+      <c r="B17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="23"/>
+      <c r="D17" s="19" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="10" t="s">
-        <v>29</v>
+        <v>16</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
